--- a/data/usuarios.xlsx
+++ b/data/usuarios.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -531,9 +531,20 @@
         <v>ADMIN</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Saray</v>
+      </c>
+      <c r="B13" t="str">
+        <v>12345</v>
+      </c>
+      <c r="C13" t="str">
+        <v>VENDEDOR</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/usuarios.xlsx
+++ b/data/usuarios.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -412,7 +412,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Laura</v>
+        <v>Juanita</v>
       </c>
       <c r="B2" t="str">
         <v>1234</v>
@@ -423,21 +423,21 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Juanita</v>
+        <v>Jorge</v>
       </c>
       <c r="B3" t="str">
-        <v>1234</v>
+        <v>jorgenel@2026</v>
       </c>
       <c r="C3" t="str">
-        <v>VENDEDOR</v>
+        <v>ADMIN</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Jorge</v>
+        <v>Stiven</v>
       </c>
       <c r="B4" t="str">
-        <v>jorgenel@2026</v>
+        <v>1234</v>
       </c>
       <c r="C4" t="str">
         <v>ADMIN</v>
@@ -445,40 +445,40 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Stiven</v>
+        <v>jhojan</v>
       </c>
       <c r="B5" t="str">
         <v>1234</v>
       </c>
       <c r="C5" t="str">
-        <v>ADMIN</v>
+        <v>VENDEDOR</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>jhojan</v>
+        <v>Luisa-Dreisy</v>
       </c>
       <c r="B6" t="str">
-        <v>1234</v>
+        <v>12345</v>
       </c>
       <c r="C6" t="str">
-        <v>VENDEDOR</v>
+        <v>ADMIN</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Luisa-Dreisy</v>
+        <v>Valeria</v>
       </c>
       <c r="B7" t="str">
-        <v>12345</v>
+        <v>1234</v>
       </c>
       <c r="C7" t="str">
-        <v>ADMIN</v>
+        <v>VENDEDOR</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Valeria</v>
+        <v>Fredy</v>
       </c>
       <c r="B8" t="str">
         <v>1234</v>
@@ -489,62 +489,73 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Fredy</v>
+        <v>Dianis</v>
       </c>
       <c r="B9" t="str">
-        <v>1234</v>
+        <v>12345</v>
       </c>
       <c r="C9" t="str">
-        <v>VENDEDOR</v>
+        <v>ADMIN</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Dianis</v>
+        <v>Alexander</v>
       </c>
       <c r="B10" t="str">
-        <v>12345</v>
+        <v>1234</v>
       </c>
       <c r="C10" t="str">
-        <v>ADMIN</v>
+        <v>VENDEDOR</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Alexander</v>
+        <v>Martha</v>
       </c>
       <c r="B11" t="str">
         <v>1234</v>
       </c>
       <c r="C11" t="str">
-        <v>VENDEDOR</v>
+        <v>ADMIN</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Martha</v>
+        <v>Saray</v>
       </c>
       <c r="B12" t="str">
-        <v>1234</v>
+        <v>12345</v>
       </c>
       <c r="C12" t="str">
-        <v>ADMIN</v>
+        <v>VENDEDOR</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Saray</v>
+        <v>juan</v>
       </c>
       <c r="B13" t="str">
-        <v>12345</v>
+        <v>1234</v>
       </c>
       <c r="C13" t="str">
+        <v>ADMIN</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Martha2</v>
+      </c>
+      <c r="B14" t="str">
+        <v>1234</v>
+      </c>
+      <c r="C14" t="str">
         <v>VENDEDOR</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/usuarios.xlsx
+++ b/data/usuarios.xlsx
@@ -525,7 +525,7 @@
         <v>Saray</v>
       </c>
       <c r="B12" t="str">
-        <v>12345</v>
+        <v>1234</v>
       </c>
       <c r="C12" t="str">
         <v>VENDEDOR</v>

--- a/data/usuarios.xlsx
+++ b/data/usuarios.xlsx
@@ -511,7 +511,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Martha</v>
+        <v>MarthaC</v>
       </c>
       <c r="B11" t="str">
         <v>1234</v>
